--- a/introductoryExamples/analysis/2-1-w2--trust.xlsx
+++ b/introductoryExamples/analysis/2-1-w2--trust.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Time</t>
   </si>
@@ -24,6 +24,12 @@
   </si>
   <si>
     <t>#Rep</t>
+  </si>
+  <si>
+    <t>fTi</t>
+  </si>
+  <si>
+    <t>fTa</t>
   </si>
   <si>
     <t>only version 2 has the problem</t>
@@ -380,21 +386,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="2.8984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="63.89453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="1.8984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="1.8984375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="5.31640625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.31640625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="5.31640625" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.31640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="2.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="65.59375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="1.9296875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="1.9296875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="5.03125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="13.03125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="5.03125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="13.03125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -410,51 +416,59 @@
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="F1" s="0"/>
+      <c r="E1" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="G1" t="s" s="12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="0"/>
       <c r="I1" t="s" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="0"/>
       <c r="K1" t="s" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L1" s="0"/>
+      <c r="M1" t="s" s="12">
+        <v>23</v>
+      </c>
+      <c r="N1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="0"/>
       <c r="B2" s="0"/>
       <c r="C2" s="0"/>
       <c r="D2" s="0"/>
-      <c r="E2" t="s" s="13">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>18</v>
-      </c>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s" s="13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="M2" t="s" s="13">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +476,7 @@
         <v>-1.0</v>
       </c>
       <c r="B3" t="s" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -470,11 +484,11 @@
       <c r="D3" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E3" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F3" t="n" s="5">
-        <v>1.0</v>
+      <c r="E3" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F3" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G3" t="n" s="15">
         <v>1.0</v>
@@ -492,6 +506,12 @@
         <v>1.0</v>
       </c>
       <c r="L3" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M3" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="N3" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -500,7 +520,7 @@
         <v>1.0</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>1.0</v>
@@ -508,28 +528,34 @@
       <c r="D4" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E4" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F4" t="n" s="5">
+      <c r="E4" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F4" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="G4" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="H4" t="n" s="5">
         <v>0.16666662693023682</v>
       </c>
-      <c r="G4" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H4" t="n" s="6">
+      <c r="I4" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="n" s="6">
         <v>-0.3333333134651184</v>
       </c>
-      <c r="I4" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J4" t="n" s="5">
+      <c r="K4" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="L4" t="n" s="5">
         <v>0.16666662693023682</v>
       </c>
-      <c r="K4" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L4" t="n" s="6">
+      <c r="M4" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="n" s="6">
         <v>-0.3333333134651184</v>
       </c>
     </row>
@@ -538,7 +564,7 @@
         <v>1.0</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -546,28 +572,34 @@
       <c r="D5" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E5" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F5" t="n" s="5">
-        <v>1.0</v>
+      <c r="E5" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F5" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G5" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H5" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I5" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L5" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M5" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -576,7 +608,7 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>3.0</v>
@@ -584,28 +616,34 @@
       <c r="D6" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E6" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F6" t="n" s="5">
-        <v>1.0</v>
+      <c r="E6" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F6" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G6" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H6" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I6" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n" s="5">
         <v>0.5833333134651184</v>
       </c>
-      <c r="I6" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J6" t="n" s="5">
-        <v>1.0</v>
-      </c>
       <c r="K6" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L6" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M6" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N6" t="n" s="5">
         <v>0.5833333134651184</v>
       </c>
     </row>
@@ -614,7 +652,7 @@
         <v>7.0</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -622,28 +660,34 @@
       <c r="D7" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E7" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F7" t="n" s="5">
-        <v>1.0</v>
+      <c r="E7" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F7" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G7" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H7" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I7" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L7" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M7" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -652,7 +696,7 @@
         <v>9.0</v>
       </c>
       <c r="B8" t="s" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -660,28 +704,34 @@
       <c r="D8" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E8" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F8" t="n" s="7">
-        <v>0.0</v>
+      <c r="E8" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F8" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G8" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H8" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H8" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n" s="6">
         <v>-0.5</v>
       </c>
-      <c r="I8" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J8" t="n" s="7">
-        <v>0.0</v>
-      </c>
       <c r="K8" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L8" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L8" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="n" s="6">
         <v>-0.5</v>
       </c>
     </row>
@@ -690,7 +740,7 @@
         <v>11.0</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>2.0</v>
@@ -698,28 +748,34 @@
       <c r="D9" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E9" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F9" t="n" s="5">
-        <v>1.0</v>
+      <c r="E9" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F9" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G9" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H9" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="I9" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="K9" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L9" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M9" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -728,7 +784,7 @@
         <v>13.0</v>
       </c>
       <c r="B10" t="s" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -736,28 +792,34 @@
       <c r="D10" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E10" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F10" t="n" s="5">
-        <v>1.0</v>
+      <c r="E10" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F10" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G10" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H10" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I10" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L10" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M10" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N10" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -766,7 +828,7 @@
         <v>13.0</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>1.0</v>
@@ -774,28 +836,34 @@
       <c r="D11" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E11" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F11" t="n" s="5">
-        <v>1.0</v>
+      <c r="E11" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F11" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G11" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H11" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="I11" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="K11" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L11" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M11" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N11" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -804,7 +872,7 @@
         <v>15.0</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -812,28 +880,34 @@
       <c r="D12" t="n" s="0">
         <v>3.0</v>
       </c>
-      <c r="E12" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F12" t="n" s="6">
+      <c r="E12" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F12" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="G12" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="H12" t="n" s="6">
         <v>-0.75</v>
       </c>
-      <c r="G12" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="n" s="6">
+      <c r="I12" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J12" t="n" s="6">
         <v>-0.25</v>
       </c>
-      <c r="I12" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J12" t="n" s="6">
+      <c r="K12" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="L12" t="n" s="6">
         <v>-0.75</v>
       </c>
-      <c r="K12" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L12" t="n" s="6">
+      <c r="M12" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N12" t="n" s="6">
         <v>-0.25</v>
       </c>
     </row>
@@ -842,7 +916,7 @@
         <v>17.0</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>1.0</v>
@@ -850,28 +924,34 @@
       <c r="D13" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E13" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F13" t="n" s="7">
-        <v>0.0</v>
+      <c r="E13" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F13" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G13" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H13" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I13" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n" s="6">
         <v>-0.08333331346511841</v>
       </c>
-      <c r="I13" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J13" t="n" s="7">
-        <v>0.0</v>
-      </c>
       <c r="K13" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L13" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L13" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N13" t="n" s="6">
         <v>-0.08333331346511841</v>
       </c>
     </row>
@@ -880,7 +960,7 @@
         <v>21.0</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -888,41 +968,49 @@
       <c r="D14" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E14" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F14" t="n" s="5">
-        <v>1.0</v>
+      <c r="E14" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F14" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G14" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H14" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I14" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n" s="5">
         <v>0.5833333134651184</v>
       </c>
-      <c r="I14" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J14" t="n" s="5">
-        <v>1.0</v>
-      </c>
       <c r="K14" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L14" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M14" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N14" t="n" s="5">
         <v>0.5833333134651184</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/introductoryExamples/analysis/2-1-w2--trust.xlsx
+++ b/introductoryExamples/analysis/2-1-w2--trust.xlsx
@@ -158,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -265,11 +265,18 @@
         <color rgb="00000000"/>
       </left>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -324,6 +331,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -907,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.7651767839435721</v>
+        <v>0.2206144962191219</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.5895675372936895</v>
+        <v>0.4300409710410276</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>1</v>
@@ -937,28 +947,28 @@
         <v>1</v>
       </c>
       <c r="O3" s="19" t="n">
-        <v>-1.765176783943572</v>
+        <v>-0.7793855037808781</v>
       </c>
       <c r="P3" s="18" t="n">
-        <v>-1.589567537293689</v>
+        <v>-0.5699590289589724</v>
       </c>
       <c r="Q3" s="19" t="n">
-        <v>-1.765176783943572</v>
+        <v>-0.7793855037808781</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>-1.589567537293689</v>
+        <v>-0.5699590289589724</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>-1.765176783943572</v>
+        <v>-0.7793855037808781</v>
       </c>
       <c r="T3" s="18" t="n">
-        <v>-1.589567537293689</v>
+        <v>-0.5699590289589724</v>
       </c>
       <c r="U3" s="19" t="n">
-        <v>-1.765176783943572</v>
+        <v>-0.7793855037808781</v>
       </c>
       <c r="V3" s="18" t="n">
-        <v>-1.589567537293689</v>
+        <v>-0.5699590289589724</v>
       </c>
     </row>
     <row r="4">
@@ -977,10 +987,10 @@
         <v>2</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>-0.02913987779191451</v>
+        <v>0.573900973627107</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>-0.1425847800800222</v>
+        <v>0.3274934085277934</v>
       </c>
       <c r="G4" s="15" t="n">
         <v>1</v>
@@ -1007,28 +1017,28 @@
         <v>-0.3333333134651184</v>
       </c>
       <c r="O4" s="19" t="n">
-        <v>-0.1958065047221513</v>
+        <v>0.4072343466968702</v>
       </c>
       <c r="P4" s="18" t="n">
-        <v>-0.309251407010259</v>
+        <v>0.1608267815975566</v>
       </c>
       <c r="Q4" s="19" t="n">
-        <v>0.3041934356732039</v>
+        <v>0.9072342870922254</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.1907485333850962</v>
+        <v>0.6608267219929118</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>-0.1958065047221513</v>
+        <v>0.4072343466968702</v>
       </c>
       <c r="T4" s="18" t="n">
-        <v>-0.309251407010259</v>
+        <v>0.1608267815975566</v>
       </c>
       <c r="U4" s="19" t="n">
-        <v>0.3041934356732039</v>
+        <v>0.9072342870922254</v>
       </c>
       <c r="V4" s="18" t="n">
-        <v>0.1907485333850962</v>
+        <v>0.6608267219929118</v>
       </c>
     </row>
     <row r="5">
@@ -1047,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.8933046032687462</v>
+        <v>-0.5573813954990416</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.6276158447420253</v>
+        <v>-0.5712151591335328</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>1</v>
@@ -1077,28 +1087,28 @@
         <v>0.5</v>
       </c>
       <c r="O5" s="19" t="n">
-        <v>-1.893304603268746</v>
+        <v>-1.557381395499042</v>
       </c>
       <c r="P5" s="18" t="n">
-        <v>-1.627615844742025</v>
+        <v>-1.571215159133533</v>
       </c>
       <c r="Q5" s="19" t="n">
-        <v>-1.393304603268746</v>
+        <v>-1.057381395499042</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>-1.127615844742025</v>
+        <v>-1.071215159133533</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>-1.893304603268746</v>
+        <v>-1.557381395499042</v>
       </c>
       <c r="T5" s="18" t="n">
-        <v>-1.627615844742025</v>
+        <v>-1.571215159133533</v>
       </c>
       <c r="U5" s="19" t="n">
-        <v>-1.393304603268746</v>
+        <v>-1.057381395499042</v>
       </c>
       <c r="V5" s="18" t="n">
-        <v>-1.127615844742025</v>
+        <v>-1.071215159133533</v>
       </c>
     </row>
     <row r="6">
@@ -1117,10 +1127,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.2352524508373357</v>
+        <v>0.8597713829475055</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>-0.4067406970874141</v>
+        <v>-0.8702709647060092</v>
       </c>
       <c r="G6" s="15" t="n">
         <v>1</v>
@@ -1147,28 +1157,28 @@
         <v>0.5833333134651184</v>
       </c>
       <c r="O6" s="19" t="n">
-        <v>-0.7647475491626643</v>
+        <v>-0.1402286170524945</v>
       </c>
       <c r="P6" s="18" t="n">
-        <v>-1.406740697087414</v>
+        <v>-1.870270964706009</v>
       </c>
       <c r="Q6" s="19" t="n">
-        <v>-0.3480808626277827</v>
+        <v>0.2764380694823871</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>-0.9900740105525325</v>
+        <v>-1.453604278171128</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>-0.7647475491626643</v>
+        <v>-0.1402286170524945</v>
       </c>
       <c r="T6" s="18" t="n">
-        <v>-1.406740697087414</v>
+        <v>-1.870270964706009</v>
       </c>
       <c r="U6" s="19" t="n">
-        <v>-0.3480808626277827</v>
+        <v>0.2764380694823871</v>
       </c>
       <c r="V6" s="18" t="n">
-        <v>-0.9900740105525325</v>
+        <v>-1.453604278171128</v>
       </c>
     </row>
     <row r="7">
@@ -1187,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.3744484475206276</v>
+        <v>0.2247974075887715</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.3971621628709838</v>
+        <v>0.3114312855247723</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>1</v>
@@ -1217,28 +1227,28 @@
         <v>0.5</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>-0.6255515524793724</v>
+        <v>-0.7752025924112285</v>
       </c>
       <c r="P7" s="18" t="n">
-        <v>-1.397162162870984</v>
+        <v>-0.6885687144752277</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>-0.1255515524793724</v>
+        <v>-0.2752025924112285</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>-0.8971621628709838</v>
+        <v>-0.1885687144752277</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>-0.6255515524793724</v>
+        <v>-0.7752025924112285</v>
       </c>
       <c r="T7" s="18" t="n">
-        <v>-1.397162162870984</v>
+        <v>-0.6885687144752277</v>
       </c>
       <c r="U7" s="19" t="n">
-        <v>-0.1255515524793724</v>
+        <v>-0.2752025924112285</v>
       </c>
       <c r="V7" s="18" t="n">
-        <v>-0.8971621628709838</v>
+        <v>-0.1885687144752277</v>
       </c>
     </row>
     <row r="8">
@@ -1257,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.05614397123895709</v>
+        <v>-0.7603838699560883</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.109053838085807</v>
+        <v>0.2925885987249655</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>1</v>
@@ -1287,28 +1297,28 @@
         <v>-0.5</v>
       </c>
       <c r="O8" s="19" t="n">
-        <v>0.05614397123895709</v>
+        <v>-0.7603838699560883</v>
       </c>
       <c r="P8" s="18" t="n">
-        <v>0.109053838085807</v>
+        <v>0.2925885987249655</v>
       </c>
       <c r="Q8" s="19" t="n">
-        <v>0.5561439712389571</v>
+        <v>-0.2603838699560883</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.609053838085807</v>
+        <v>0.7925885987249655</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.05614397123895709</v>
+        <v>-0.7603838699560883</v>
       </c>
       <c r="T8" s="18" t="n">
-        <v>0.109053838085807</v>
+        <v>0.2925885987249655</v>
       </c>
       <c r="U8" s="19" t="n">
-        <v>0.5561439712389571</v>
+        <v>-0.2603838699560883</v>
       </c>
       <c r="V8" s="18" t="n">
-        <v>0.609053838085807</v>
+        <v>0.7925885987249655</v>
       </c>
     </row>
     <row r="9">
@@ -1327,10 +1337,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.6800041549984421</v>
+        <v>-0.7410914807164353</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.4729599788500125</v>
+        <v>-0.01955006787579228</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>1</v>
@@ -1357,28 +1367,28 @@
         <v>1</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>-1.680004154998442</v>
+        <v>-1.741091480716435</v>
       </c>
       <c r="P9" s="18" t="n">
-        <v>-1.472959978850013</v>
+        <v>-1.019550067875792</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>-1.680004154998442</v>
+        <v>-1.741091480716435</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>-1.472959978850013</v>
+        <v>-1.019550067875792</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>-1.680004154998442</v>
+        <v>-1.741091480716435</v>
       </c>
       <c r="T9" s="18" t="n">
-        <v>-1.472959978850013</v>
+        <v>-1.019550067875792</v>
       </c>
       <c r="U9" s="19" t="n">
-        <v>-1.680004154998442</v>
+        <v>-1.741091480716435</v>
       </c>
       <c r="V9" s="18" t="n">
-        <v>-1.472959978850013</v>
+        <v>-1.019550067875792</v>
       </c>
     </row>
     <row r="10">
@@ -1397,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.7009000800928504</v>
+        <v>0.7573745161048473</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>-0.1085735997305262</v>
+        <v>-0.498730030279015</v>
       </c>
       <c r="G10" s="15" t="n">
         <v>1</v>
@@ -1427,28 +1437,28 @@
         <v>0.5</v>
       </c>
       <c r="O10" s="19" t="n">
-        <v>-0.2990999199071496</v>
+        <v>-0.2426254838951527</v>
       </c>
       <c r="P10" s="18" t="n">
-        <v>-1.108573599730526</v>
+        <v>-1.498730030279015</v>
       </c>
       <c r="Q10" s="19" t="n">
-        <v>0.2009000800928504</v>
+        <v>0.2573745161048473</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>-0.6085735997305262</v>
+        <v>-0.998730030279015</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>-0.2990999199071496</v>
+        <v>-0.2426254838951527</v>
       </c>
       <c r="T10" s="18" t="n">
-        <v>-1.108573599730526</v>
+        <v>-1.498730030279015</v>
       </c>
       <c r="U10" s="19" t="n">
-        <v>0.2009000800928504</v>
+        <v>0.2573745161048473</v>
       </c>
       <c r="V10" s="18" t="n">
-        <v>-0.6085735997305262</v>
+        <v>-0.998730030279015</v>
       </c>
     </row>
     <row r="11">
@@ -1467,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.7522152302668796</v>
+        <v>-0.08865232357216812</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.4094978036435579</v>
+        <v>-0.9915271337533917</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>1</v>
@@ -1497,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>-1.75221523026688</v>
+        <v>-1.088652323572168</v>
       </c>
       <c r="P11" s="18" t="n">
-        <v>-0.5905021963564421</v>
+        <v>-1.991527133753392</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>-1.75221523026688</v>
+        <v>-1.088652323572168</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>-0.5905021963564421</v>
+        <v>-1.991527133753392</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>-1.75221523026688</v>
+        <v>-1.088652323572168</v>
       </c>
       <c r="T11" s="18" t="n">
-        <v>-0.5905021963564421</v>
+        <v>-1.991527133753392</v>
       </c>
       <c r="U11" s="19" t="n">
-        <v>-1.75221523026688</v>
+        <v>-1.088652323572168</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>-0.5905021963564421</v>
+        <v>-1.991527133753392</v>
       </c>
     </row>
     <row r="12">
@@ -1537,10 +1547,10 @@
         <v>3</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.3235367733002175</v>
+        <v>-0.6369940928405768</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.9290335826726537</v>
+        <v>-0.6297259374655644</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>1</v>
@@ -1567,28 +1577,28 @@
         <v>-0.25</v>
       </c>
       <c r="O12" s="19" t="n">
-        <v>1.073536773300217</v>
+        <v>0.1130059071594232</v>
       </c>
       <c r="P12" s="18" t="n">
-        <v>1.679033582672654</v>
+        <v>0.1202740625344356</v>
       </c>
       <c r="Q12" s="19" t="n">
-        <v>0.5735367733002175</v>
+        <v>-0.3869940928405768</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.179033582672654</v>
+        <v>-0.3797259374655644</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.073536773300217</v>
+        <v>0.1130059071594232</v>
       </c>
       <c r="T12" s="18" t="n">
-        <v>1.679033582672654</v>
+        <v>0.1202740625344356</v>
       </c>
       <c r="U12" s="19" t="n">
-        <v>0.5735367733002175</v>
+        <v>-0.3869940928405768</v>
       </c>
       <c r="V12" s="18" t="n">
-        <v>1.179033582672654</v>
+        <v>-0.3797259374655644</v>
       </c>
     </row>
     <row r="13">
@@ -1607,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.03976178922493045</v>
+        <v>-0.7520509940042073</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.6324943519428661</v>
+        <v>0.9704919313585636</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>1</v>
@@ -1637,28 +1647,28 @@
         <v>-0.08333331346511841</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>0.03976178922493045</v>
+        <v>-0.7520509940042073</v>
       </c>
       <c r="P13" s="18" t="n">
-        <v>0.6324943519428661</v>
+        <v>0.9704919313585636</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>0.1230951026900489</v>
+        <v>-0.6687176805390889</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.7158276654079845</v>
+        <v>1.053825244823682</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.03976178922493045</v>
+        <v>-0.7520509940042073</v>
       </c>
       <c r="T13" s="18" t="n">
-        <v>0.6324943519428661</v>
+        <v>0.9704919313585636</v>
       </c>
       <c r="U13" s="19" t="n">
-        <v>0.1230951026900489</v>
+        <v>-0.6687176805390889</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>0.7158276654079845</v>
+        <v>1.053825244823682</v>
       </c>
     </row>
     <row r="14">
@@ -1677,10 +1687,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>-0.1758993958809423</v>
+        <v>0.6740908577426226</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>-0.7250891374097437</v>
+        <v>-0.08686562177785517</v>
       </c>
       <c r="G14" s="15" t="n">
         <v>1</v>
@@ -1707,28 +1717,28 @@
         <v>0.5833333134651184</v>
       </c>
       <c r="O14" s="19" t="n">
-        <v>-1.175899395880942</v>
+        <v>-0.3259091422573774</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>-1.725089137409744</v>
+        <v>-1.086865621777855</v>
       </c>
       <c r="Q14" s="19" t="n">
-        <v>-0.7592327093460607</v>
+        <v>0.09075754427750415</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>-1.308422450874862</v>
+        <v>-0.6701989352429736</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>-1.175899395880942</v>
+        <v>-0.3259091422573774</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>-1.725089137409744</v>
+        <v>-1.086865621777855</v>
       </c>
       <c r="U14" s="19" t="n">
-        <v>-0.7592327093460607</v>
+        <v>0.09075754427750415</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>-1.308422450874862</v>
+        <v>-0.6701989352429736</v>
       </c>
     </row>
   </sheetData>
@@ -1761,6 +1771,30 @@
     <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
       <formula>NOT(ISNUMBER(O3:E14))</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="0" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="1" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="2" stopIfTrue="1">
+      <formula>NOT(ISNUMBER(O3:E14))</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="0" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="1" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="2" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="2" stopIfTrue="1">
+      <formula>NOT(ISNUMBER(O3:E14))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:V14">
     <cfRule type="cellIs" priority="5" operator="notBetween" dxfId="0" stopIfTrue="1">
@@ -1774,6 +1808,28 @@
     <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="1">
       <formula>NOT(ISNUMBER(O3:V14))</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="12" operator="notBetween" dxfId="0" stopIfTrue="1">
+      <formula>-0.5</formula>
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="between" dxfId="1" stopIfTrue="1">
+      <formula>-0.5</formula>
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="2" stopIfTrue="1">
+      <formula>NOT(ISNUMBER(O3:V14))</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="notBetween" dxfId="0" stopIfTrue="1">
+      <formula>-0.5</formula>
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="between" dxfId="1" stopIfTrue="1">
+      <formula>-0.5</formula>
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
+      <formula>NOT(ISNUMBER(O3:V14))</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
